--- a/templates/GDA-FLC-003_materia_organica.xlsx
+++ b/templates/GDA-FLC-003_materia_organica.xlsx
@@ -3503,7 +3503,7 @@
         <v>39</v>
       </c>
       <c r="I23" s="162" t="str">
-        <f>+IF(I19=0,"",(I19-I20)/(I20-I21)*100)</f>
+        <f>+IF(I19=0,"",(I19-I20)/(I19-I21)*100)</f>
         <v/>
       </c>
       <c r="J23" s="163"/>
